--- a/cwa_classroom/brainbuzz/management/commands/samples/sample_maths_questions.xlsx
+++ b/cwa_classroom/brainbuzz/management/commands/samples/sample_maths_questions.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -542,15 +542,15 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fractions</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>What is 1/2 + 1/4?</t>
+          <t>What is the area of a parallelogram with base 8 cm and height 5 cm?</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -566,33 +566,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>To add fractions, find a common denominator. 1/2 = 2/4, so 2/4 + 1/4 = 3/4.</t>
+          <t>Area of parallelogram = base × height = 8 × 5 = 40 cm².</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>13 cm²</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>40 cm²</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>true</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>26 cm²</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>20 cm²</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -614,92 +614,108 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fractions</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Is 3/6 equivalent to 1/2?</t>
+          <t>What is the area of a circle with radius 7 cm? (Use π ≈ 3.14)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>true_false</t>
+          <t>multiple_choice</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>3/6 simplifies to 1/2 by dividing numerator and denominator by 3.</t>
+          <t>Area = π × r² = 3.14 × 7² = 3.14 × 49 ≈ 153.86 cm².</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>43.96 cm²</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>153.86 cm²</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>true</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>98 cm²</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>21.98 cm²</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Fractions</t>
+          <t>Perimeter</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Simplify the fraction 12/16 to its lowest terms.</t>
+          <t>Fill in the blank: Perimeter of a square with side 6 cm = ___ cm.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>short_answer</t>
+          <t>fill_blank</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>The GCF of 12 and 16 is 4. Dividing both by 4 gives 3/4.</t>
+          <t>Perimeter of square = 4 × side = 4 × 6 = 24 cm.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -714,15 +730,15 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Perimeter</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>What is 7 × 8?</t>
+          <t>What is the perimeter of a triangle with sides 5 cm, 7 cm, and 9 cm?</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -738,13 +754,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>7 × 8 = 56.</t>
+          <t>Perimeter = sum of all sides = 5 + 7 + 9 = 21 cm.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19 cm</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -754,7 +770,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>21 cm</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -764,7 +780,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>23 cm</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -774,7 +790,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63 cm</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -786,15 +802,15 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Division is the inverse (opposite) of multiplication.</t>
+          <t>Probability of an event always lies between 0 and 1 inclusive.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -810,7 +826,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>If a × b = c then c ÷ b = a.</t>
+          <t>P = 0 means impossible, P = 1 means certain. All probabilities lie in [0, 1].</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -842,59 +858,87 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>A store sells apples for $0.35 each. How much do 12 apples cost?</t>
+          <t>What is the probability of rolling a 4 on a fair six-sided die?</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>short_answer</t>
+          <t>multiple_choice</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>12 × $0.35 = $4.20</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>$4.20</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
+          <t>There is 1 favourable outcome out of 6 equally likely outcomes. P = 1/6.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>1/6</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BODMAS</t>
+          <t>Linear Equations</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Evaluate: 3 + 4 × 2 − 1</t>
+          <t>Solve: 2x − 3 = x + 5</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -910,33 +954,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>BODMAS: multiplication first → 4 × 2 = 8, then 3 + 8 − 1 = 10.</t>
+          <t>Subtract x from both sides: x − 3 = 5. Add 3: x = 8.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>true</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -946,7 +990,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>−8</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -958,15 +1002,15 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Linear Equations</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Solve for x: 2x + 5 = 13</t>
+          <t>Solve: 3(x − 2) = 9</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -982,12 +1026,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Subtract 5 from both sides: 2x = 8. Divide by 2: x = 4.</t>
+          <t>Expand: 3x − 6 = 9. Add 6: 3x = 15. Divide by 3: x = 5.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -1002,15 +1046,15 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Integers</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Which of the following is equivalent to 3(x + 4)?</t>
+          <t>What is −5 + 8?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1019,40 +1063,40 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Distribute: 3(x + 4) = 3x + 12.</t>
+          <t>Start at −5 and count up 8: −5 + 8 = 3.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3x + 12</t>
+          <t>−3</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>true</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3x + 4</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>x + 12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1062,7 +1106,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3x + 7</t>
+          <t>−13</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1074,15 +1118,15 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Addition</t>
+          <t>Integers</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>What is 5 + 3?</t>
+          <t>What is −3 × −4?</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1091,42 +1135,42 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Count on from 5: 6, 7, 8. So 5 + 3 = 8.</t>
+          <t>Negative × Negative = Positive. −3 × −4 = 12.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t>−12</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>false</t>
@@ -1134,7 +1178,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>−7</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1146,46 +1190,434 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Addition</t>
+          <t>Prime Numbers</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Which of these is a prime number?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>multiple_choice</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Fill in the blank: 14 + ___ = 20</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>fill_blank</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20 − 14 = 6. So the missing number is 6.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+          <t>23 is divisible only by 1 and itself. 21=3×7, 25=5×5, 27=3×9.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Prime Numbers</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>1 is a prime number.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>true_false</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>By definition, a prime number has exactly 2 distinct factors. 1 has only 1 factor. False.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Square Roots</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>What is √144?</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>multiple_choice</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12 × 12 = 144. So √144 = 12.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Square Roots</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>What is √225?</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>short_answer</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>15 × 15 = 225. So √225 = 15.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BODMAS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Evaluate: (2 + 3)² − 4 × 3 + 1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>multiple_choice</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Brackets: (2+3)=5. Power: 5²=25. Multiply: 4×3=12. Then: 25 − 12 + 1 = 14.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Fractions</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Convert 1 3/4 to an improper fraction.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>short_answer</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>(1 × 4) + 3 = 7. Denominator stays 4. Answer: 7/4.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>7/4</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Round 4,672 to the nearest hundred.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>multiple_choice</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Tens digit is 7 (≥5), so round up. 4,672 → 4,700.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
